--- a/tests/golden/non_table.xlsx
+++ b/tests/golden/non_table.xlsx
@@ -722,7 +722,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -991,7 +991,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1001,18 +1000,12 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1028,9 +1021,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="11" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1061,13 +1051,9 @@
     <xf numFmtId="168" fontId="15" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1152,405 +1138,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>368546</colOff>
-      <row>14</row>
-      <rowOff>60977</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="圖片 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="982980" y="617220"/>
-          <a:ext cx="1587746" cy="1584977"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>3</col>
-      <colOff>147566</colOff>
-      <row>13</row>
-      <rowOff>144797</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="圖片 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="982980" y="617220"/>
-          <a:ext cx="1587746" cy="1584977"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>22860</colOff>
-      <row>10</row>
-      <rowOff>22860</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>541086</colOff>
-      <row>16</row>
-      <rowOff>180804</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="圖片 2"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="922020" y="2415540"/>
-          <a:ext cx="1478346" cy="1300944"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>1</col>
-      <colOff>495300</colOff>
-      <row>0</row>
-      <rowOff>160020</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1242060</colOff>
-      <row>0</row>
-      <rowOff>906780</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="圖片 6"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="762000" y="160020"/>
-          <a:ext cx="746760" cy="746760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>327660</colOff>
-      <row>13</row>
-      <rowOff>9754</rowOff>
-    </from>
-    <to>
-      <col>10</col>
-      <colOff>899226</colOff>
-      <row>19</row>
-      <rowOff>76258</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="圖片 8"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="8702040" y="3804514"/>
-          <a:ext cx="1478346" cy="1300944"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>1477449</colOff>
-      <row>15</row>
-      <rowOff>40588</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="圖片 1"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="1593273" y="1870364"/>
-          <a:ext cx="1477449" cy="1287497"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>8</col>
-      <colOff>202830</colOff>
-      <row>15</row>
-      <rowOff>40588</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="圖片 2"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="10044545" y="1870364"/>
-          <a:ext cx="1477449" cy="1287497"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>15240</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>1219200</colOff>
-      <row>0</row>
-      <rowOff>1203960</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="圖片 3"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="15240" y="0"/>
-          <a:ext cx="1203960" cy="1203960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>6</col>
-      <colOff>298333</colOff>
-      <row>33</row>
-      <rowOff>66504</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="圖片 4"/>
-        <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm>
-          <a:off x="7717971" y="6770914"/>
-          <a:ext cx="1473991" cy="1307476"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1910,74 +1497,74 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="104" t="inlineStr">
+      <c r="A3" s="103" t="inlineStr">
         <is>
           <t>張三</t>
         </is>
       </c>
-      <c r="B3" s="104" t="n">
+      <c r="B3" s="103" t="n">
         <v>25</v>
       </c>
-      <c r="C3" s="104" t="inlineStr">
+      <c r="C3" s="103" t="inlineStr">
         <is>
           <t>技術部</t>
         </is>
       </c>
-      <c r="D3" s="104" t="n">
+      <c r="D3" s="103" t="n">
         <v>50000</v>
       </c>
-      <c r="E3" s="104" t="n">
+      <c r="E3" s="103" t="n">
         <v>5000</v>
       </c>
-      <c r="F3" s="104" t="n">
+      <c r="F3" s="103" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="104" t="inlineStr">
+      <c r="A4" s="103" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B4" s="104" t="n">
+      <c r="B4" s="103" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="103" t="inlineStr">
         <is>
           <t>業務部</t>
         </is>
       </c>
-      <c r="D4" s="104" t="n">
+      <c r="D4" s="103" t="n">
         <v>55000</v>
       </c>
-      <c r="E4" s="104" t="n">
+      <c r="E4" s="103" t="n">
         <v>6000</v>
       </c>
-      <c r="F4" s="104" t="n">
+      <c r="F4" s="103" t="n">
         <v>61000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="104" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="B5" s="104" t="n">
+      <c r="B5" s="103" t="n">
         <v>35</v>
       </c>
-      <c r="C5" s="104" t="inlineStr">
+      <c r="C5" s="103" t="inlineStr">
         <is>
           <t>人事部</t>
         </is>
       </c>
-      <c r="D5" s="104" t="n">
+      <c r="D5" s="103" t="n">
         <v>60000</v>
       </c>
-      <c r="E5" s="104" t="n">
+      <c r="E5" s="103" t="n">
         <v>7000</v>
       </c>
-      <c r="F5" s="104" t="n">
+      <c r="F5" s="103" t="n">
         <v>67000</v>
       </c>
     </row>
@@ -2167,7 +1754,7 @@
           <t>信義區</t>
         </is>
       </c>
-      <c r="C10" s="129" t="n">
+      <c r="C10" s="124" t="n">
         <v>2000000</v>
       </c>
       <c r="D10" s="108" t="n">
@@ -2194,7 +1781,7 @@
           <t>大安區</t>
         </is>
       </c>
-      <c r="C11" s="129" t="n">
+      <c r="C11" s="124" t="n">
         <v>1800000</v>
       </c>
       <c r="D11" s="108" t="n">
@@ -2209,22 +1796,6 @@
       <c r="G11" s="108" t="n">
         <v>-36000</v>
       </c>
-      <c r="H11" s="130" t="n"/>
-      <c r="I11" s="130" t="n"/>
-      <c r="J11" s="130" t="n"/>
-      <c r="K11" s="130" t="n"/>
-      <c r="L11" s="130" t="n"/>
-      <c r="M11" s="130" t="n"/>
-      <c r="N11" s="130" t="n"/>
-      <c r="O11" s="130" t="n"/>
-      <c r="P11" s="130" t="n"/>
-      <c r="Q11" s="130" t="n"/>
-      <c r="R11" s="130" t="n"/>
-      <c r="S11" s="130" t="n"/>
-      <c r="T11" s="130" t="n"/>
-      <c r="U11" s="130" t="n"/>
-      <c r="V11" s="130" t="n"/>
-      <c r="W11" s="130" t="n"/>
     </row>
     <row r="12" ht="36.6" customFormat="1" customHeight="1" s="94">
       <c r="A12" s="108" t="inlineStr">
@@ -2237,7 +1808,7 @@
           <t>中山區</t>
         </is>
       </c>
-      <c r="C12" s="129" t="n">
+      <c r="C12" s="124" t="n">
         <v>2200000</v>
       </c>
       <c r="D12" s="108" t="n">
@@ -2252,22 +1823,6 @@
       <c r="G12" s="108" t="n">
         <v>-44000</v>
       </c>
-      <c r="H12" s="130" t="n"/>
-      <c r="I12" s="130" t="n"/>
-      <c r="J12" s="130" t="n"/>
-      <c r="K12" s="130" t="n"/>
-      <c r="L12" s="130" t="n"/>
-      <c r="M12" s="130" t="n"/>
-      <c r="N12" s="130" t="n"/>
-      <c r="O12" s="130" t="n"/>
-      <c r="P12" s="130" t="n"/>
-      <c r="Q12" s="130" t="n"/>
-      <c r="R12" s="130" t="n"/>
-      <c r="S12" s="130" t="n"/>
-      <c r="T12" s="130" t="n"/>
-      <c r="U12" s="130" t="n"/>
-      <c r="V12" s="130" t="n"/>
-      <c r="W12" s="130" t="n"/>
     </row>
     <row r="13" ht="33.9" customHeight="1" s="1"/>
     <row r="14" ht="17.1" customHeight="1" s="1">
@@ -2345,7 +1900,7 @@
           <t>信義區</t>
         </is>
       </c>
-      <c r="C17" s="129" t="n">
+      <c r="C17" s="124" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="108" t="n">
@@ -2366,7 +1921,7 @@
           <t>大安區</t>
         </is>
       </c>
-      <c r="C18" s="129" t="n">
+      <c r="C18" s="124" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="108" t="inlineStr">
@@ -2377,22 +1932,6 @@
       <c r="E18" s="32" t="n"/>
       <c r="F18" s="92" t="n"/>
       <c r="G18" s="92" t="n"/>
-      <c r="H18" s="130" t="n"/>
-      <c r="I18" s="130" t="n"/>
-      <c r="J18" s="130" t="n"/>
-      <c r="K18" s="130" t="n"/>
-      <c r="L18" s="130" t="n"/>
-      <c r="M18" s="130" t="n"/>
-      <c r="N18" s="130" t="n"/>
-      <c r="O18" s="130" t="n"/>
-      <c r="P18" s="130" t="n"/>
-      <c r="Q18" s="130" t="n"/>
-      <c r="R18" s="130" t="n"/>
-      <c r="S18" s="130" t="n"/>
-      <c r="T18" s="130" t="n"/>
-      <c r="U18" s="130" t="n"/>
-      <c r="V18" s="130" t="n"/>
-      <c r="W18" s="130" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="108" t="inlineStr">
@@ -2405,7 +1944,7 @@
           <t>中山區</t>
         </is>
       </c>
-      <c r="C19" s="129" t="n">
+      <c r="C19" s="124" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="108" t="n">
@@ -2414,29 +1953,13 @@
       <c r="E19" s="32" t="n"/>
       <c r="F19" s="92" t="n"/>
       <c r="G19" s="92" t="n"/>
-      <c r="H19" s="130" t="n"/>
-      <c r="I19" s="130" t="n"/>
-      <c r="J19" s="130" t="n"/>
-      <c r="K19" s="130" t="n"/>
-      <c r="L19" s="130" t="n"/>
-      <c r="M19" s="130" t="n"/>
-      <c r="N19" s="130" t="n"/>
-      <c r="O19" s="130" t="n"/>
-      <c r="P19" s="130" t="n"/>
-      <c r="Q19" s="130" t="n"/>
-      <c r="R19" s="130" t="n"/>
-      <c r="S19" s="130" t="n"/>
-      <c r="T19" s="130" t="n"/>
-      <c r="U19" s="130" t="n"/>
-      <c r="V19" s="130" t="n"/>
-      <c r="W19" s="130" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="92" t="n"/>
-      <c r="C20" s="131" t="n"/>
-      <c r="E20" s="132" t="n"/>
-      <c r="F20" s="132" t="n"/>
-      <c r="G20" s="132" t="n"/>
+      <c r="C20" s="125" t="n"/>
+      <c r="E20" s="126" t="n"/>
+      <c r="F20" s="126" t="n"/>
+      <c r="G20" s="126" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="93" t="inlineStr">
@@ -2525,20 +2048,6 @@
       <c r="G25" s="92" t="n"/>
       <c r="H25" s="92" t="n"/>
       <c r="I25" s="92" t="n"/>
-      <c r="J25" s="130" t="n"/>
-      <c r="K25" s="130" t="n"/>
-      <c r="L25" s="130" t="n"/>
-      <c r="M25" s="130" t="n"/>
-      <c r="N25" s="130" t="n"/>
-      <c r="O25" s="130" t="n"/>
-      <c r="P25" s="130" t="n"/>
-      <c r="Q25" s="130" t="n"/>
-      <c r="R25" s="130" t="n"/>
-      <c r="S25" s="130" t="n"/>
-      <c r="T25" s="130" t="n"/>
-      <c r="U25" s="130" t="n"/>
-      <c r="V25" s="130" t="n"/>
-      <c r="W25" s="130" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="108" t="inlineStr">
@@ -2560,20 +2069,6 @@
       <c r="G26" s="92" t="n"/>
       <c r="H26" s="92" t="n"/>
       <c r="I26" s="92" t="n"/>
-      <c r="J26" s="130" t="n"/>
-      <c r="K26" s="130" t="n"/>
-      <c r="L26" s="130" t="n"/>
-      <c r="M26" s="130" t="n"/>
-      <c r="N26" s="130" t="n"/>
-      <c r="O26" s="130" t="n"/>
-      <c r="P26" s="130" t="n"/>
-      <c r="Q26" s="130" t="n"/>
-      <c r="R26" s="130" t="n"/>
-      <c r="S26" s="130" t="n"/>
-      <c r="T26" s="130" t="n"/>
-      <c r="U26" s="130" t="n"/>
-      <c r="V26" s="130" t="n"/>
-      <c r="W26" s="130" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="92" t="n"/>
@@ -2643,7 +2138,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2738,51 +2232,51 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="104" t="inlineStr">
+      <c r="A4" s="103" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B4" s="104" t="n">
+      <c r="B4" s="103" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="103" t="inlineStr">
         <is>
           <t>業務部</t>
         </is>
       </c>
-      <c r="D4" s="104" t="n">
+      <c r="D4" s="103" t="n">
         <v>55000</v>
       </c>
-      <c r="E4" s="104" t="n">
+      <c r="E4" s="103" t="n">
         <v>6000</v>
       </c>
-      <c r="F4" s="104">
+      <c r="F4" s="103">
         <f>D4+E4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="104" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="B5" s="104" t="n">
+      <c r="B5" s="103" t="n">
         <v>35</v>
       </c>
-      <c r="C5" s="104" t="inlineStr">
+      <c r="C5" s="103" t="inlineStr">
         <is>
           <t>人事部</t>
         </is>
       </c>
-      <c r="D5" s="104" t="n">
+      <c r="D5" s="103" t="n">
         <v>60000</v>
       </c>
-      <c r="E5" s="104" t="n">
+      <c r="E5" s="103" t="n">
         <v>7000</v>
       </c>
-      <c r="F5" s="104">
+      <c r="F5" s="103">
         <f>D5+E5</f>
         <v/>
       </c>
@@ -2855,74 +2349,74 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="104" t="inlineStr">
+      <c r="A3" s="103" t="inlineStr">
         <is>
           <t>張三</t>
         </is>
       </c>
-      <c r="B3" s="104" t="n">
+      <c r="B3" s="103" t="n">
         <v>25</v>
       </c>
-      <c r="C3" s="104" t="inlineStr">
+      <c r="C3" s="103" t="inlineStr">
         <is>
           <t>技術部</t>
         </is>
       </c>
-      <c r="D3" s="104" t="n">
+      <c r="D3" s="103" t="n">
         <v>50000</v>
       </c>
-      <c r="E3" s="104" t="n">
+      <c r="E3" s="103" t="n">
         <v>5000</v>
       </c>
-      <c r="F3" s="104" t="n">
+      <c r="F3" s="103" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="1">
-      <c r="A4" s="104" t="inlineStr">
+      <c r="A4" s="103" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B4" s="104" t="n">
+      <c r="B4" s="103" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="103" t="inlineStr">
         <is>
           <t>業務部</t>
         </is>
       </c>
-      <c r="D4" s="104" t="n">
+      <c r="D4" s="103" t="n">
         <v>55000</v>
       </c>
-      <c r="E4" s="104" t="n">
+      <c r="E4" s="103" t="n">
         <v>6000</v>
       </c>
-      <c r="F4" s="104" t="n">
+      <c r="F4" s="103" t="n">
         <v>61000</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="1">
-      <c r="A5" s="104" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="B5" s="104" t="n">
+      <c r="B5" s="103" t="n">
         <v>35</v>
       </c>
-      <c r="C5" s="104" t="inlineStr">
+      <c r="C5" s="103" t="inlineStr">
         <is>
           <t>人事部</t>
         </is>
       </c>
-      <c r="D5" s="104" t="n">
+      <c r="D5" s="103" t="n">
         <v>60000</v>
       </c>
-      <c r="E5" s="104" t="n">
+      <c r="E5" s="103" t="n">
         <v>7000</v>
       </c>
-      <c r="F5" s="104" t="n">
+      <c r="F5" s="103" t="n">
         <v>67000</v>
       </c>
     </row>
@@ -2938,7 +2432,6 @@
     <row r="9" ht="15" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3033,51 +2526,51 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="104" t="inlineStr">
+      <c r="A4" s="103" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B4" s="104" t="n">
+      <c r="B4" s="103" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="103" t="inlineStr">
         <is>
           <t>業務部</t>
         </is>
       </c>
-      <c r="D4" s="104" t="n">
+      <c r="D4" s="103" t="n">
         <v>55000</v>
       </c>
-      <c r="E4" s="104" t="n">
+      <c r="E4" s="103" t="n">
         <v>6000</v>
       </c>
-      <c r="F4" s="104">
+      <c r="F4" s="103">
         <f>D4+E4</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="1">
-      <c r="A5" s="104" t="inlineStr">
+      <c r="A5" s="103" t="inlineStr">
         <is>
           <t>王五</t>
         </is>
       </c>
-      <c r="B5" s="104" t="n">
+      <c r="B5" s="103" t="n">
         <v>35</v>
       </c>
-      <c r="C5" s="104" t="inlineStr">
+      <c r="C5" s="103" t="inlineStr">
         <is>
           <t>人事部</t>
         </is>
       </c>
-      <c r="D5" s="104" t="n">
+      <c r="D5" s="103" t="n">
         <v>60000</v>
       </c>
-      <c r="E5" s="104" t="n">
+      <c r="E5" s="103" t="n">
         <v>7000</v>
       </c>
-      <c r="F5" s="104">
+      <c r="F5" s="103">
         <f>D5+E5</f>
         <v/>
       </c>
@@ -3094,7 +2587,6 @@
     <row r="9" ht="15" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3339,104 +2831,104 @@
       </c>
     </row>
     <row r="6" ht="16.2" customHeight="1" s="1">
-      <c r="A6" s="105" t="inlineStr">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>紅線</t>
         </is>
       </c>
-      <c r="B6" s="106" t="n">
+      <c r="B6" s="105" t="n">
         <v>1200</v>
       </c>
-      <c r="C6" s="107" t="n">
+      <c r="C6" s="106" t="n">
         <v>24000</v>
       </c>
-      <c r="D6" s="106" t="n">
+      <c r="D6" s="105" t="n">
         <v>300</v>
       </c>
-      <c r="E6" s="107" t="n">
+      <c r="E6" s="106" t="n">
         <v>6000</v>
       </c>
-      <c r="F6" s="106" t="n">
+      <c r="F6" s="105" t="n">
         <v>150</v>
       </c>
-      <c r="G6" s="107" t="n">
+      <c r="G6" s="106" t="n">
         <v>3000</v>
       </c>
-      <c r="H6" s="106" t="n">
+      <c r="H6" s="105" t="n">
         <v>80</v>
       </c>
-      <c r="I6" s="107" t="n">
+      <c r="I6" s="106" t="n">
         <v>1600</v>
       </c>
-      <c r="J6" s="107" t="n">
+      <c r="J6" s="106" t="n">
         <v>34600</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="108" t="inlineStr">
+      <c r="A7" s="104" t="inlineStr">
         <is>
           <t>藍線</t>
         </is>
       </c>
-      <c r="B7" s="109" t="n">
+      <c r="B7" s="105" t="n">
         <v>980</v>
       </c>
-      <c r="C7" s="110" t="n">
+      <c r="C7" s="106" t="n">
         <v>19600</v>
       </c>
-      <c r="D7" s="109" t="n">
+      <c r="D7" s="105" t="n">
         <v>250</v>
       </c>
-      <c r="E7" s="110" t="n">
+      <c r="E7" s="106" t="n">
         <v>5000</v>
       </c>
-      <c r="F7" s="109" t="n">
+      <c r="F7" s="105" t="n">
         <v>120</v>
       </c>
-      <c r="G7" s="110" t="n">
+      <c r="G7" s="106" t="n">
         <v>2400</v>
       </c>
-      <c r="H7" s="109" t="n">
+      <c r="H7" s="105" t="n">
         <v>60</v>
       </c>
-      <c r="I7" s="110" t="n">
+      <c r="I7" s="106" t="n">
         <v>1200</v>
       </c>
-      <c r="J7" s="110" t="n">
+      <c r="J7" s="106" t="n">
         <v>28200</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="108" t="inlineStr">
+      <c r="A8" s="104" t="inlineStr">
         <is>
           <t>綠線</t>
         </is>
       </c>
-      <c r="B8" s="109" t="n">
+      <c r="B8" s="105" t="n">
         <v>1150</v>
       </c>
-      <c r="C8" s="110" t="n">
+      <c r="C8" s="106" t="n">
         <v>23000</v>
       </c>
-      <c r="D8" s="109" t="n">
+      <c r="D8" s="105" t="n">
         <v>320</v>
       </c>
-      <c r="E8" s="110" t="n">
+      <c r="E8" s="106" t="n">
         <v>6400</v>
       </c>
-      <c r="F8" s="109" t="n">
+      <c r="F8" s="105" t="n">
         <v>180</v>
       </c>
-      <c r="G8" s="110" t="n">
+      <c r="G8" s="106" t="n">
         <v>3600</v>
       </c>
-      <c r="H8" s="109" t="n">
+      <c r="H8" s="105" t="n">
         <v>90</v>
       </c>
-      <c r="I8" s="110" t="n">
+      <c r="I8" s="106" t="n">
         <v>1800</v>
       </c>
-      <c r="J8" s="110" t="n">
+      <c r="J8" s="106" t="n">
         <v>34800</v>
       </c>
     </row>
@@ -3452,7 +2944,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3622,7 +3113,7 @@
           <t>金額(G1)</t>
         </is>
       </c>
-      <c r="K8" s="111" t="inlineStr">
+      <c r="K8" s="107" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
@@ -3640,28 +3131,28 @@
           <t>中央區</t>
         </is>
       </c>
-      <c r="D9" s="112" t="n">
+      <c r="D9" s="109" t="n">
         <v>0.3</v>
       </c>
-      <c r="E9" s="113" t="n">
+      <c r="E9" s="110" t="n">
         <v>1200</v>
       </c>
-      <c r="F9" s="114" t="n">
+      <c r="F9" s="111" t="n">
         <v>1500000</v>
       </c>
-      <c r="G9" s="114" t="n">
+      <c r="G9" s="111" t="n">
         <v>1260000</v>
       </c>
-      <c r="H9" s="114" t="n">
+      <c r="H9" s="111" t="n">
         <v>240000</v>
       </c>
-      <c r="I9" s="115" t="n">
+      <c r="I9" s="112" t="n">
         <v>0.6</v>
       </c>
-      <c r="J9" s="114" t="n">
+      <c r="J9" s="111" t="n">
         <v>144000</v>
       </c>
-      <c r="K9" s="116" t="n">
+      <c r="K9" s="113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3677,28 +3168,28 @@
           <t>東區</t>
         </is>
       </c>
-      <c r="D10" s="112" t="n">
+      <c r="D10" s="109" t="n">
         <v>0.25</v>
       </c>
-      <c r="E10" s="113" t="n">
+      <c r="E10" s="110" t="n">
         <v>980</v>
       </c>
-      <c r="F10" s="114" t="n">
+      <c r="F10" s="111" t="n">
         <v>1200000</v>
       </c>
-      <c r="G10" s="114" t="n">
+      <c r="G10" s="111" t="n">
         <v>1050000</v>
       </c>
-      <c r="H10" s="114" t="n">
+      <c r="H10" s="111" t="n">
         <v>150000</v>
       </c>
-      <c r="I10" s="115" t="n">
+      <c r="I10" s="112" t="n">
         <v>0.6</v>
       </c>
-      <c r="J10" s="114" t="n">
+      <c r="J10" s="111" t="n">
         <v>90000</v>
       </c>
-      <c r="K10" s="117" t="n">
+      <c r="K10" s="113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3714,28 +3205,28 @@
           <t>西區</t>
         </is>
       </c>
-      <c r="D11" s="112" t="n">
+      <c r="D11" s="109" t="n">
         <v>0.45</v>
       </c>
-      <c r="E11" s="113" t="n">
+      <c r="E11" s="110" t="n">
         <v>1350</v>
       </c>
-      <c r="F11" s="114" t="n">
+      <c r="F11" s="111" t="n">
         <v>1800000</v>
       </c>
-      <c r="G11" s="114" t="n">
+      <c r="G11" s="111" t="n">
         <v>1890000</v>
       </c>
-      <c r="H11" s="114" t="n">
+      <c r="H11" s="111" t="n">
         <v>-90000</v>
       </c>
-      <c r="I11" s="115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="117" t="n">
+      <c r="I11" s="112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4001,7 +3492,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4064,32 +3554,32 @@
           <t>路線名稱</t>
         </is>
       </c>
-      <c r="D2" s="118" t="inlineStr">
+      <c r="D2" s="114" t="inlineStr">
         <is>
           <t>學生刷卡旅次量
 A=IC學生票刷卡量</t>
         </is>
       </c>
-      <c r="E2" s="118" t="inlineStr">
+      <c r="E2" s="114" t="inlineStr">
         <is>
           <t>市民卡(學生卡)
 應收總金額(元)
 B=市民卡營收金額</t>
         </is>
       </c>
-      <c r="F2" s="118" t="inlineStr">
+      <c r="F2" s="114" t="inlineStr">
         <is>
           <t>市民卡(學生卡)
 實際營收金額(元)
 C=學生票營收金額</t>
         </is>
       </c>
-      <c r="G2" s="119" t="inlineStr">
+      <c r="G2" s="115" t="inlineStr">
         <is>
           <t>市民卡(學生卡)基本里程優惠金額(元)D</t>
         </is>
       </c>
-      <c r="H2" s="120" t="inlineStr">
+      <c r="H2" s="116" t="inlineStr">
         <is>
           <t>票價上限補貼金額(元)E</t>
         </is>
@@ -4122,143 +3612,143 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="121" t="inlineStr">
+      <c r="A3" s="117" t="inlineStr">
         <is>
           <t>R001</t>
         </is>
       </c>
-      <c r="B3" s="121" t="inlineStr">
+      <c r="B3" s="117" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="C3" s="122" t="inlineStr">
+      <c r="C3" s="118" t="inlineStr">
         <is>
           <t>市中心線</t>
         </is>
       </c>
-      <c r="D3" s="123" t="n">
+      <c r="D3" s="119" t="n">
         <v>2500</v>
       </c>
-      <c r="E3" s="123" t="n">
+      <c r="E3" s="119" t="n">
         <v>125000</v>
       </c>
-      <c r="F3" s="123" t="n">
+      <c r="F3" s="119" t="n">
         <v>100000</v>
       </c>
-      <c r="G3" s="123" t="n">
+      <c r="G3" s="119" t="n">
         <v>12500</v>
       </c>
-      <c r="H3" s="123" t="n">
+      <c r="H3" s="119" t="n">
         <v>7500</v>
       </c>
-      <c r="I3" s="123" t="n">
+      <c r="I3" s="119" t="n">
         <v>5000</v>
       </c>
-      <c r="J3" s="124" t="n">
+      <c r="J3" s="120" t="n">
         <v>3000</v>
       </c>
-      <c r="K3" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="124" t="n">
+      <c r="K3" s="120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="120" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="16.8" customHeight="1" s="1" thickBot="1">
-      <c r="A4" s="121" t="inlineStr">
+      <c r="A4" s="117" t="inlineStr">
         <is>
           <t>R002</t>
         </is>
       </c>
-      <c r="B4" s="121" t="inlineStr">
+      <c r="B4" s="117" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="C4" s="122" t="inlineStr">
+      <c r="C4" s="118" t="inlineStr">
         <is>
           <t>工業區線</t>
         </is>
       </c>
-      <c r="D4" s="123" t="n">
+      <c r="D4" s="119" t="n">
         <v>1800</v>
       </c>
-      <c r="E4" s="123" t="n">
+      <c r="E4" s="119" t="n">
         <v>90000</v>
       </c>
-      <c r="F4" s="123" t="n">
+      <c r="F4" s="119" t="n">
         <v>72000</v>
       </c>
-      <c r="G4" s="123" t="n">
+      <c r="G4" s="119" t="n">
         <v>9000</v>
       </c>
-      <c r="H4" s="123" t="n">
+      <c r="H4" s="119" t="n">
         <v>5400</v>
       </c>
-      <c r="I4" s="123" t="n">
+      <c r="I4" s="119" t="n">
         <v>3600</v>
       </c>
-      <c r="J4" s="124" t="n">
+      <c r="J4" s="120" t="n">
         <v>2160</v>
       </c>
-      <c r="K4" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="124" t="n">
+      <c r="K4" s="120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="120" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="121" t="inlineStr">
+      <c r="A5" s="117" t="inlineStr">
         <is>
           <t>R003</t>
         </is>
       </c>
-      <c r="B5" s="121" t="inlineStr">
+      <c r="B5" s="117" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="C5" s="122" t="inlineStr">
+      <c r="C5" s="118" t="inlineStr">
         <is>
           <t>住宅區線</t>
         </is>
       </c>
-      <c r="D5" s="123" t="n">
+      <c r="D5" s="119" t="n">
         <v>2200</v>
       </c>
-      <c r="E5" s="123" t="n">
+      <c r="E5" s="119" t="n">
         <v>110000</v>
       </c>
-      <c r="F5" s="123" t="n">
+      <c r="F5" s="119" t="n">
         <v>88000</v>
       </c>
-      <c r="G5" s="123" t="n">
+      <c r="G5" s="119" t="n">
         <v>11000</v>
       </c>
-      <c r="H5" s="123" t="n">
+      <c r="H5" s="119" t="n">
         <v>6600</v>
       </c>
-      <c r="I5" s="123" t="n">
+      <c r="I5" s="119" t="n">
         <v>4400</v>
       </c>
-      <c r="J5" s="124" t="n">
+      <c r="J5" s="120" t="n">
         <v>2640</v>
       </c>
-      <c r="K5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="124" t="n">
+      <c r="K5" s="120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4270,54 +3760,54 @@
       </c>
       <c r="B6" s="85" t="n"/>
       <c r="C6" s="86" t="n"/>
-      <c r="D6" s="125">
+      <c r="D6" s="121">
         <f>SUM(D3:D3)</f>
         <v/>
       </c>
-      <c r="E6" s="125">
+      <c r="E6" s="121">
         <f>SUM(E3:E3)</f>
         <v/>
       </c>
-      <c r="F6" s="125">
+      <c r="F6" s="121">
         <f>SUM(F3:F3)</f>
         <v/>
       </c>
-      <c r="G6" s="125">
+      <c r="G6" s="121">
         <f>SUM(G3:G3)</f>
         <v/>
       </c>
-      <c r="H6" s="125">
+      <c r="H6" s="121">
         <f>SUM(H3:H3)</f>
         <v/>
       </c>
-      <c r="I6" s="125">
+      <c r="I6" s="121">
         <f>SUM(I3:I3)</f>
         <v/>
       </c>
-      <c r="J6" s="125">
+      <c r="J6" s="121">
         <f>SUM(J3:J3)</f>
         <v/>
       </c>
-      <c r="K6" s="125">
+      <c r="K6" s="121">
         <f>SUM(K3:K3)</f>
         <v/>
       </c>
-      <c r="L6" s="125">
+      <c r="L6" s="121">
         <f>SUM(L3:L3)</f>
         <v/>
       </c>
-      <c r="M6" s="125">
+      <c r="M6" s="121">
         <f>SUM(M3:M3)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="71" t="n"/>
-      <c r="G7" s="126" t="n"/>
+      <c r="G7" s="122" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="71" t="n"/>
-      <c r="I8" s="126" t="n"/>
+      <c r="I8" s="122" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="71" t="n"/>
@@ -4392,7 +3882,7 @@
     <row r="53"/>
     <row r="54"/>
     <row r="55">
-      <c r="D55" s="126" t="n"/>
+      <c r="D55" s="122" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4401,7 +3891,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4540,131 +4029,131 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="127" t="inlineStr">
+      <c r="A4" s="123" t="inlineStr">
         <is>
           <t>65-74</t>
         </is>
       </c>
-      <c r="B4" s="127" t="n">
+      <c r="B4" s="123" t="n">
         <v>1200</v>
       </c>
-      <c r="C4" s="127" t="n">
+      <c r="C4" s="123" t="n">
         <v>24000</v>
       </c>
-      <c r="D4" s="127" t="n">
+      <c r="D4" s="123" t="n">
         <v>150</v>
       </c>
-      <c r="E4" s="127" t="n">
+      <c r="E4" s="123" t="n">
         <v>7500</v>
       </c>
-      <c r="F4" s="127" t="n">
+      <c r="F4" s="123" t="n">
         <v>300</v>
       </c>
-      <c r="G4" s="127" t="n">
+      <c r="G4" s="123" t="n">
         <v>6000</v>
       </c>
-      <c r="H4" s="127" t="n">
+      <c r="H4" s="123" t="n">
         <v>80</v>
       </c>
-      <c r="I4" s="127" t="n">
+      <c r="I4" s="123" t="n">
         <v>1600</v>
       </c>
-      <c r="J4" s="127" t="n">
+      <c r="J4" s="123" t="n">
         <v>40</v>
       </c>
-      <c r="K4" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="127" t="n">
+      <c r="K4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="128" t="inlineStr">
+      <c r="A5" s="123" t="inlineStr">
         <is>
           <t>75-84</t>
         </is>
       </c>
-      <c r="B5" s="128" t="n">
+      <c r="B5" s="123" t="n">
         <v>800</v>
       </c>
-      <c r="C5" s="128" t="n">
+      <c r="C5" s="123" t="n">
         <v>16000</v>
       </c>
-      <c r="D5" s="128" t="n">
+      <c r="D5" s="123" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="128" t="n">
+      <c r="E5" s="123" t="n">
         <v>5000</v>
       </c>
-      <c r="F5" s="128" t="n">
+      <c r="F5" s="123" t="n">
         <v>200</v>
       </c>
-      <c r="G5" s="128" t="n">
+      <c r="G5" s="123" t="n">
         <v>4000</v>
       </c>
-      <c r="H5" s="128" t="n">
+      <c r="H5" s="123" t="n">
         <v>50</v>
       </c>
-      <c r="I5" s="128" t="n">
+      <c r="I5" s="123" t="n">
         <v>1000</v>
       </c>
-      <c r="J5" s="128" t="n">
+      <c r="J5" s="123" t="n">
         <v>25</v>
       </c>
-      <c r="K5" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="128" t="n">
+      <c r="K5" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="128" t="inlineStr">
+      <c r="A6" s="123" t="inlineStr">
         <is>
           <t>85+</t>
         </is>
       </c>
-      <c r="B6" s="128" t="n">
+      <c r="B6" s="123" t="n">
         <v>300</v>
       </c>
-      <c r="C6" s="128" t="n">
+      <c r="C6" s="123" t="n">
         <v>6000</v>
       </c>
-      <c r="D6" s="128" t="n">
+      <c r="D6" s="123" t="n">
         <v>50</v>
       </c>
-      <c r="E6" s="128" t="n">
+      <c r="E6" s="123" t="n">
         <v>2500</v>
       </c>
-      <c r="F6" s="128" t="n">
+      <c r="F6" s="123" t="n">
         <v>80</v>
       </c>
-      <c r="G6" s="128" t="n">
+      <c r="G6" s="123" t="n">
         <v>1600</v>
       </c>
-      <c r="H6" s="128" t="n">
+      <c r="H6" s="123" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="128" t="n">
+      <c r="I6" s="123" t="n">
         <v>400</v>
       </c>
-      <c r="J6" s="128" t="n">
+      <c r="J6" s="123" t="n">
         <v>10</v>
       </c>
-      <c r="K6" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="128" t="n">
+      <c r="K6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4809,131 +4298,131 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="127" t="inlineStr">
+      <c r="A11" s="123" t="inlineStr">
         <is>
           <t>65-74</t>
         </is>
       </c>
-      <c r="B11" s="127" t="n">
+      <c r="B11" s="123" t="n">
         <v>1150</v>
       </c>
-      <c r="C11" s="127" t="n">
+      <c r="C11" s="123" t="n">
         <v>23000</v>
       </c>
-      <c r="D11" s="127" t="n">
+      <c r="D11" s="123" t="n">
         <v>140</v>
       </c>
-      <c r="E11" s="127" t="n">
+      <c r="E11" s="123" t="n">
         <v>7000</v>
       </c>
-      <c r="F11" s="127" t="n">
+      <c r="F11" s="123" t="n">
         <v>280</v>
       </c>
-      <c r="G11" s="127" t="n">
+      <c r="G11" s="123" t="n">
         <v>5600</v>
       </c>
-      <c r="H11" s="127" t="n">
+      <c r="H11" s="123" t="n">
         <v>75</v>
       </c>
-      <c r="I11" s="127" t="n">
+      <c r="I11" s="123" t="n">
         <v>1500</v>
       </c>
-      <c r="J11" s="127" t="n">
+      <c r="J11" s="123" t="n">
         <v>38</v>
       </c>
-      <c r="K11" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="127" t="n">
+      <c r="K11" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="128" t="inlineStr">
+      <c r="A12" s="123" t="inlineStr">
         <is>
           <t>75-84</t>
         </is>
       </c>
-      <c r="B12" s="128" t="n">
+      <c r="B12" s="123" t="n">
         <v>750</v>
       </c>
-      <c r="C12" s="128" t="n">
+      <c r="C12" s="123" t="n">
         <v>15000</v>
       </c>
-      <c r="D12" s="128" t="n">
+      <c r="D12" s="123" t="n">
         <v>95</v>
       </c>
-      <c r="E12" s="128" t="n">
+      <c r="E12" s="123" t="n">
         <v>4750</v>
       </c>
-      <c r="F12" s="128" t="n">
+      <c r="F12" s="123" t="n">
         <v>190</v>
       </c>
-      <c r="G12" s="128" t="n">
+      <c r="G12" s="123" t="n">
         <v>3800</v>
       </c>
-      <c r="H12" s="128" t="n">
+      <c r="H12" s="123" t="n">
         <v>45</v>
       </c>
-      <c r="I12" s="128" t="n">
+      <c r="I12" s="123" t="n">
         <v>900</v>
       </c>
-      <c r="J12" s="128" t="n">
+      <c r="J12" s="123" t="n">
         <v>22</v>
       </c>
-      <c r="K12" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="128" t="n">
+      <c r="K12" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="128" t="inlineStr">
+      <c r="A13" s="123" t="inlineStr">
         <is>
           <t>85+</t>
         </is>
       </c>
-      <c r="B13" s="128" t="n">
+      <c r="B13" s="123" t="n">
         <v>280</v>
       </c>
-      <c r="C13" s="128" t="n">
+      <c r="C13" s="123" t="n">
         <v>5600</v>
       </c>
-      <c r="D13" s="128" t="n">
+      <c r="D13" s="123" t="n">
         <v>45</v>
       </c>
-      <c r="E13" s="128" t="n">
+      <c r="E13" s="123" t="n">
         <v>2250</v>
       </c>
-      <c r="F13" s="128" t="n">
+      <c r="F13" s="123" t="n">
         <v>75</v>
       </c>
-      <c r="G13" s="128" t="n">
+      <c r="G13" s="123" t="n">
         <v>1500</v>
       </c>
-      <c r="H13" s="128" t="n">
+      <c r="H13" s="123" t="n">
         <v>18</v>
       </c>
-      <c r="I13" s="128" t="n">
+      <c r="I13" s="123" t="n">
         <v>360</v>
       </c>
-      <c r="J13" s="128" t="n">
+      <c r="J13" s="123" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="128" t="n">
+      <c r="K13" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5078,131 +4567,131 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="127" t="inlineStr">
+      <c r="A18" s="123" t="inlineStr">
         <is>
           <t>65-74</t>
         </is>
       </c>
-      <c r="B18" s="127" t="n">
+      <c r="B18" s="123" t="n">
         <v>1300</v>
       </c>
-      <c r="C18" s="127" t="n">
+      <c r="C18" s="123" t="n">
         <v>26000</v>
       </c>
-      <c r="D18" s="127" t="n">
+      <c r="D18" s="123" t="n">
         <v>160</v>
       </c>
-      <c r="E18" s="127" t="n">
+      <c r="E18" s="123" t="n">
         <v>8000</v>
       </c>
-      <c r="F18" s="127" t="n">
+      <c r="F18" s="123" t="n">
         <v>320</v>
       </c>
-      <c r="G18" s="127" t="n">
+      <c r="G18" s="123" t="n">
         <v>6400</v>
       </c>
-      <c r="H18" s="127" t="n">
+      <c r="H18" s="123" t="n">
         <v>85</v>
       </c>
-      <c r="I18" s="127" t="n">
+      <c r="I18" s="123" t="n">
         <v>1700</v>
       </c>
-      <c r="J18" s="127" t="n">
+      <c r="J18" s="123" t="n">
         <v>42</v>
       </c>
-      <c r="K18" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="127" t="n">
+      <c r="K18" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="128" t="inlineStr">
+      <c r="A19" s="123" t="inlineStr">
         <is>
           <t>75-84</t>
         </is>
       </c>
-      <c r="B19" s="128" t="n">
+      <c r="B19" s="123" t="n">
         <v>850</v>
       </c>
-      <c r="C19" s="128" t="n">
+      <c r="C19" s="123" t="n">
         <v>17000</v>
       </c>
-      <c r="D19" s="128" t="n">
+      <c r="D19" s="123" t="n">
         <v>110</v>
       </c>
-      <c r="E19" s="128" t="n">
+      <c r="E19" s="123" t="n">
         <v>5500</v>
       </c>
-      <c r="F19" s="128" t="n">
+      <c r="F19" s="123" t="n">
         <v>210</v>
       </c>
-      <c r="G19" s="128" t="n">
+      <c r="G19" s="123" t="n">
         <v>4200</v>
       </c>
-      <c r="H19" s="128" t="n">
+      <c r="H19" s="123" t="n">
         <v>55</v>
       </c>
-      <c r="I19" s="128" t="n">
+      <c r="I19" s="123" t="n">
         <v>1100</v>
       </c>
-      <c r="J19" s="128" t="n">
+      <c r="J19" s="123" t="n">
         <v>28</v>
       </c>
-      <c r="K19" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="128" t="n">
+      <c r="K19" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="128" t="inlineStr">
+      <c r="A20" s="123" t="inlineStr">
         <is>
           <t>85+</t>
         </is>
       </c>
-      <c r="B20" s="128" t="n">
+      <c r="B20" s="123" t="n">
         <v>320</v>
       </c>
-      <c r="C20" s="128" t="n">
+      <c r="C20" s="123" t="n">
         <v>6400</v>
       </c>
-      <c r="D20" s="128" t="n">
+      <c r="D20" s="123" t="n">
         <v>55</v>
       </c>
-      <c r="E20" s="128" t="n">
+      <c r="E20" s="123" t="n">
         <v>2750</v>
       </c>
-      <c r="F20" s="128" t="n">
+      <c r="F20" s="123" t="n">
         <v>85</v>
       </c>
-      <c r="G20" s="128" t="n">
+      <c r="G20" s="123" t="n">
         <v>1700</v>
       </c>
-      <c r="H20" s="128" t="n">
+      <c r="H20" s="123" t="n">
         <v>22</v>
       </c>
-      <c r="I20" s="128" t="n">
+      <c r="I20" s="123" t="n">
         <v>440</v>
       </c>
-      <c r="J20" s="128" t="n">
+      <c r="J20" s="123" t="n">
         <v>12</v>
       </c>
-      <c r="K20" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="128" t="n">
+      <c r="K20" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5347,131 +4836,131 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="127" t="inlineStr">
+      <c r="A25" s="123" t="inlineStr">
         <is>
           <t>65-74</t>
         </is>
       </c>
-      <c r="B25" s="127" t="n">
+      <c r="B25" s="123" t="n">
         <v>1250</v>
       </c>
-      <c r="C25" s="127" t="n">
+      <c r="C25" s="123" t="n">
         <v>25000</v>
       </c>
-      <c r="D25" s="127" t="n">
+      <c r="D25" s="123" t="n">
         <v>155</v>
       </c>
-      <c r="E25" s="127" t="n">
+      <c r="E25" s="123" t="n">
         <v>7750</v>
       </c>
-      <c r="F25" s="127" t="n">
+      <c r="F25" s="123" t="n">
         <v>310</v>
       </c>
-      <c r="G25" s="127" t="n">
+      <c r="G25" s="123" t="n">
         <v>6200</v>
       </c>
-      <c r="H25" s="127" t="n">
+      <c r="H25" s="123" t="n">
         <v>82</v>
       </c>
-      <c r="I25" s="127" t="n">
+      <c r="I25" s="123" t="n">
         <v>1640</v>
       </c>
-      <c r="J25" s="127" t="n">
+      <c r="J25" s="123" t="n">
         <v>41</v>
       </c>
-      <c r="K25" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="127" t="n">
+      <c r="K25" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="128" t="inlineStr">
+      <c r="A26" s="123" t="inlineStr">
         <is>
           <t>75-84</t>
         </is>
       </c>
-      <c r="B26" s="128" t="n">
+      <c r="B26" s="123" t="n">
         <v>820</v>
       </c>
-      <c r="C26" s="128" t="n">
+      <c r="C26" s="123" t="n">
         <v>16400</v>
       </c>
-      <c r="D26" s="128" t="n">
+      <c r="D26" s="123" t="n">
         <v>105</v>
       </c>
-      <c r="E26" s="128" t="n">
+      <c r="E26" s="123" t="n">
         <v>5250</v>
       </c>
-      <c r="F26" s="128" t="n">
+      <c r="F26" s="123" t="n">
         <v>200</v>
       </c>
-      <c r="G26" s="128" t="n">
+      <c r="G26" s="123" t="n">
         <v>4000</v>
       </c>
-      <c r="H26" s="128" t="n">
+      <c r="H26" s="123" t="n">
         <v>52</v>
       </c>
-      <c r="I26" s="128" t="n">
+      <c r="I26" s="123" t="n">
         <v>1040</v>
       </c>
-      <c r="J26" s="128" t="n">
+      <c r="J26" s="123" t="n">
         <v>26</v>
       </c>
-      <c r="K26" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="128" t="n">
+      <c r="K26" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="123" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="128" t="inlineStr">
+      <c r="A27" s="123" t="inlineStr">
         <is>
           <t>85+</t>
         </is>
       </c>
-      <c r="B27" s="128" t="n">
+      <c r="B27" s="123" t="n">
         <v>310</v>
       </c>
-      <c r="C27" s="128" t="n">
+      <c r="C27" s="123" t="n">
         <v>6200</v>
       </c>
-      <c r="D27" s="128" t="n">
+      <c r="D27" s="123" t="n">
         <v>52</v>
       </c>
-      <c r="E27" s="128" t="n">
+      <c r="E27" s="123" t="n">
         <v>2600</v>
       </c>
-      <c r="F27" s="128" t="n">
+      <c r="F27" s="123" t="n">
         <v>82</v>
       </c>
-      <c r="G27" s="128" t="n">
+      <c r="G27" s="123" t="n">
         <v>1640</v>
       </c>
-      <c r="H27" s="128" t="n">
+      <c r="H27" s="123" t="n">
         <v>21</v>
       </c>
-      <c r="I27" s="128" t="n">
+      <c r="I27" s="123" t="n">
         <v>420</v>
       </c>
-      <c r="J27" s="128" t="n">
+      <c r="J27" s="123" t="n">
         <v>11</v>
       </c>
-      <c r="K27" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="128" t="n">
+      <c r="K27" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="123" t="n">
         <v>0</v>
       </c>
     </row>
